--- a/data/trans_camb/IP16A07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Estudios-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,14</t>
+          <t>0,0; 11,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,1</t>
+          <t>0,0; 8,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,19</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,72</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,48</t>
+          <t>0,31; 3,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,8</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Estudios-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,9</t>
+          <t>0,0; 16,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,25</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>0,0; 12,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,72</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,76</t>
+          <t>0,28; 3,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,15; 1,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir</t>
+          <t>Menores que consumieron pastillas para dormir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 16,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,54</t>
+          <t>0,0; 9,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,22 +730,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,33</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
     </row>
@@ -956,22 +956,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,68</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 6,39</t>
         </is>
       </c>
     </row>
@@ -1172,22 +1172,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1272,24 +1272,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,37; 4,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,58</t>
+          <t>0,18; 2,1</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
